--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.92.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.92.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -855,7 +855,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.92.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.92.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,8 +431,8 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.92.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.92.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0092.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0092.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -605,16 +605,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L29: stray/suspicious non-ASCII glyph(s): U+00AF MACRON :: è¯Š</t>
+          <t>L29: stray/suspicious non-ASCII glyph(s): U+8BCA CJK UNIFIED IDEOGRAPH-8BCA | isolated marker/symbol line :: 诊</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L14: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]85</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]85</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L25: isolated marker/symbol line :: 85</t>
@@ -622,7 +626,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L12: isolated marker/symbol line :: 1</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]85</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -649,7 +653,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>67</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -662,14 +666,10 @@
       </c>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L33: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: actionâ€�</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L20: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: In case an injunction to stay proceedings at law beâ€˜LXXIV.</t>
+          <t>L14: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -681,7 +681,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L14: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L12: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -717,26 +717,22 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L58: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: p Ã¦ na;</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L48: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L48: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L42: isolated marker/symbol line :: 0</t>
+          <t>L29: stray/suspicious non-ASCII glyph(s): U+8BCA CJK UNIFIED IDEOGRAPH-8BCA | isolated marker/symbol line :: 诊</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L16: isolated marker/symbol line :: 4</t>
+          <t>L14: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -758,12 +754,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -775,19 +771,19 @@
       <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L56: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: anielâ€™s</t>
+          <t>L69: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: ys from •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L72: isolated marker/symbol line :: 1</t>
+          <t>L42: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L48: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L16: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -824,21 +820,17 @@
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
       <c r="J6" s="1" t="inlineStr"/>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L69: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: ys from â€¢</t>
-        </is>
-      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L73: isolated marker/symbol line :: b</t>
+          <t>L72: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L72: isolated marker/symbol line :: a</t>
+          <t>L48: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -880,12 +872,12 @@
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L74: isolated marker/symbol line :: 3</t>
+          <t>L73: isolated marker/symbol line :: b</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L74: isolated marker/symbol line :: -</t>
+          <t>L72: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -927,12 +919,12 @@
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L75: isolated marker/symbol line :: 9</t>
+          <t>L74: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L76: isolated marker/symbol line :: I</t>
+          <t>L74: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -972,10 +964,14 @@
       <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
-      <c r="N9" s="1" t="inlineStr"/>
+      <c r="N9" s="1" t="inlineStr">
+        <is>
+          <t>L75: isolated marker/symbol line :: 9</t>
+        </is>
+      </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L90: isolated marker/symbol line :: #</t>
+          <t>L76: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -997,12 +993,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1018,7 +1014,7 @@
       <c r="N10" s="1" t="inlineStr"/>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L92: isolated marker/symbol line :: 9</t>
+          <t>L90: isolated marker/symbol line :: #</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1045,7 +1041,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1059,7 +1055,11 @@
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr"/>
-      <c r="O11" s="1" t="inlineStr"/>
+      <c r="O11" s="1" t="inlineStr">
+        <is>
+          <t>L92: isolated marker/symbol line :: 9</t>
+        </is>
+      </c>
       <c r="P11" s="1" t="inlineStr"/>
       <c r="Q11" s="1" t="inlineStr"/>
       <c r="R11" s="1" t="inlineStr"/>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
